--- a/it_forms/002_it_room_weekly_inspection_checklist--it_forms.xlsx
+++ b/it_forms/002_it_room_weekly_inspection_checklist--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1118,8 +1118,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'secure',_'value':_'secure'}</t>
+          <t>secure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Secure', 'value': 'Secure'}</t>
+          <t>Secure</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_secure',_'value':_'not_secure'}</t>
+          <t>not_secure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Secure', 'value': 'Not Secure'}</t>
+          <t>Not Secure</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
